--- a/Data/EXCEL/Transfer/bzPerformance/20250413PAP/1602-bzPerformance_perAndPbr20250413PAP.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/20250413PAP/1602-bzPerformance_perAndPbr20250413PAP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20250413PAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\20250413PAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CF5217C-54CB-4D25-AD3E-75777E0E1B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21DF3FEC-B25D-44C7-84FC-873DD8BA4AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{C07256AA-EF2F-4AF5-A6EC-B1C4C1D4CEEE}"/>
+    <workbookView xWindow="1800" yWindow="840" windowWidth="17640" windowHeight="14310" xr2:uid="{D8823668-9023-4A16-B38E-D1700516730E}"/>
   </bookViews>
   <sheets>
     <sheet name="1602-bzPerformance_perAndPbr202" sheetId="2" r:id="rId1"/>
@@ -1250,19 +1250,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCB93B14-D741-4836-A1DA-7451BA692732}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF896F1B-642F-4FAE-9A65-22752B63CFB0}">
   <dimension ref="A1:Q36"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="9" width="11.77734375" customWidth="1"/>
-    <col min="10" max="10" width="12.21875" customWidth="1"/>
-    <col min="11" max="13" width="11.77734375" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" customWidth="1"/>
-    <col min="15" max="16" width="11.77734375" customWidth="1"/>
-    <col min="17" max="17" width="12.21875" customWidth="1"/>
+    <col min="1" max="9" width="8.6328125" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" customWidth="1"/>
+    <col min="11" max="13" width="8.6328125" customWidth="1"/>
+    <col min="14" max="14" width="9.08984375" customWidth="1"/>
+    <col min="15" max="16" width="8.6328125" customWidth="1"/>
+    <col min="17" max="17" width="9.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1293,7 +1293,7 @@
       <c r="P1" s="17"/>
       <c r="Q1" s="18"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A2" s="14"/>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -1344,7 +1344,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="15"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1381,7 +1381,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>19</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A5" s="9">
         <v>2023</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>2022</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A7" s="9">
         <v>2021</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>2020</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A9" s="9">
         <v>2019</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>2018</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A11" s="9">
         <v>2017</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>2016</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A13" s="9">
         <v>2015</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>2014</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A15" s="9">
         <v>2013</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A16" s="6">
         <v>2012</v>
       </c>
@@ -2070,7 +2070,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A17" s="9">
         <v>2011</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A18" s="6">
         <v>2010</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A19" s="9">
         <v>2009</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A20" s="6">
         <v>2008</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A21" s="9">
         <v>2007</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A22" s="6">
         <v>2006</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A23" s="9">
         <v>2005</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A24" s="6">
         <v>2004</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A25" s="9">
         <v>2003</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A26" s="6">
         <v>2002</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A27" s="9">
         <v>2001</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A28" s="6">
         <v>2000</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A29" s="9">
         <v>1999</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A30" s="6">
         <v>1998</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A31" s="9">
         <v>1997</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A32" s="6">
         <v>1996</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A33" s="9">
         <v>1995</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A34" s="6">
         <v>1994</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" s="8" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A35" s="9">
         <v>1990</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A36" s="6">
         <v>1989</v>
       </c>
